--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_intro.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_intro.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_前情提要" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="380">
   <si>
     <t>ID</t>
   </si>
@@ -87,9 +87,15 @@
     <t>前情提要——</t>
   </si>
   <si>
+    <t>18 enhanced_APPLE</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
+    <t>unlockmusic(Music18)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=0</t>
   </si>
   <si>
@@ -99,7 +105,7 @@
     <t>一周前，身为联邦调查局探员的你们接到了一个由FBI分局指派的任务，任务要求你们潜入一家名为“圣诺汀”的废弃精神病院，回收代号为“盖亚之心”的科技造物。</t>
   </si>
   <si>
-    <t>bgfade(mainmenu,1)</t>
+    <t>bgfade(mainmenu1,1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=1</t>
@@ -138,7 +144,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>choice(是|jump(9))&amp;choice(不是|jump(8))</t>
+    <t>choice(是|jump(7))&amp;choice(不是|jump(8))</t>
   </si>
   <si>
     <t>源类型=type:selectBC; 层级=5</t>
@@ -147,7 +153,10 @@
     <t>7</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=6</t>
+    <t>jump(9)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=6; tag=告知</t>
   </si>
   <si>
     <t>9</t>
@@ -159,7 +168,7 @@
     <t>bgfade(sntzm_main2_61,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=7; tag=告知</t>
+    <t>源类型=type:txt_pb; 层级=7</t>
   </si>
   <si>
     <t>10</t>
@@ -174,7 +183,7 @@
     <t>11</t>
   </si>
   <si>
-    <t>choice(追上飞蛾|jump(15))&amp;choice(接听无线电|jump(13))</t>
+    <t>choice(追上飞蛾|jump(12))&amp;choice(接听无线电|jump(13))</t>
   </si>
   <si>
     <t>源类型=type:selectBC; 层级=9</t>
@@ -183,7 +192,10 @@
     <t>12</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=10</t>
+    <t>jump(14)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=10; tag=飞蛾线</t>
   </si>
   <si>
     <t>14</t>
@@ -201,7 +213,7 @@
     <t>jump(17)&amp;bgfade(sntzm_fe_9,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=12; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"飞蛾线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=17; tag=飞蛾线</t>
+    <t>源类型=type:txt_pb; 层级=12; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"飞蛾线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=17</t>
   </si>
   <si>
     <t>16</t>
@@ -228,7 +240,7 @@
     <t>18</t>
   </si>
   <si>
-    <t>choice(跟上克拉克|jump(21))&amp;choice(与大卫随行|jump(20))</t>
+    <t>choice(跟上克拉克|jump(19))&amp;choice(与大卫随行|jump(20))</t>
   </si>
   <si>
     <t>源类型=type:selectBC; 层级=14</t>
@@ -237,7 +249,10 @@
     <t>19</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=15</t>
+    <t>jump(21)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=15; tag=克拉克线</t>
   </si>
   <si>
     <t>21</t>
@@ -249,7 +264,7 @@
     <t>bgfade(sntzm_main3_41,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=16; tag=克拉克线</t>
+    <t>源类型=type:txt_pb; 层级=16</t>
   </si>
   <si>
     <t>22</t>
@@ -282,7 +297,78 @@
     <t>27</t>
   </si>
   <si>
-    <t>在向前探索的过程中，你们仔细调查了一间编号为B2-07的病房，先是在房间的角落找到了一只刻有“艾米莉.沃德森”的铭牌，紧接着又在放门外发现了一颗疑似属于大卫的子弹。</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在向前探索的过程中，你们仔细调查了一间编号为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>B2-07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的病房，先是在房间的角落找到了一只刻有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>艾米丽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>沃德森</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的铭牌，紧接着又在放门外发现了一颗疑似属于大卫的子弹。</t>
+    </r>
   </si>
   <si>
     <t>bgfade(sntzm_clark2_13,1)&amp;bgfade(sntzm_clark3_6,1)</t>
@@ -318,7 +404,30 @@
     <t>32</t>
   </si>
   <si>
-    <t>男孩对艾米莉.沃德森的铭牌表现出了巨大的偏执，加之大卫的失踪显然和他有关。你们便以铭牌为要挟对其进行了一番审问，你还记得当时自己问了什么吗？</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>男孩对艾米丽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>沃德森的铭牌表现出了巨大的偏执，加之大卫的失踪显然和他有关。你们便以铭牌为要挟对其进行了一番审问，你还记得当时自己问了什么吗？</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=23</t>
@@ -327,7 +436,46 @@
     <t>33</t>
   </si>
   <si>
-    <t>choice(询问了关于大卫的问题|jump(36))&amp;choice(询问了关于艾米莉的问题|jump(37))</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>choice(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>询问了关于大卫的问题</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|jump(34))&amp;choice(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>询问了关于艾米丽的问题</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|jump(35))</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:selectBC; 层级=24</t>
@@ -336,7 +484,49 @@
     <t>34</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=25</t>
+    <t>jump(36)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=25; tag=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>问大卫</t>
+    </r>
   </si>
   <si>
     <t>36</t>
@@ -348,7 +538,7 @@
     <t>bgfade(sntzm_clark5_41,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=26; tag=问大卫</t>
+    <t>源类型=type:txt_pb; 层级=26</t>
   </si>
   <si>
     <t>39</t>
@@ -372,7 +562,7 @@
     <t>41</t>
   </si>
   <si>
-    <t>choice(开枪击中他的肩膀|jump(46))&amp;choice(开枪故意射偏|jump(47))</t>
+    <t>choice(开枪击中他的肩膀|jump(42))&amp;choice(开枪故意射偏|jump(43))</t>
   </si>
   <si>
     <t>源类型=type:selectBC; 层级=29</t>
@@ -381,7 +571,10 @@
     <t>42</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=30</t>
+    <t>jump(46)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=30; tag=开枪</t>
   </si>
   <si>
     <t>46</t>
@@ -390,67 +583,21 @@
     <t>你的果断换来了亚波伦的欣赏，他按照约定自称放走了大卫，但也提前透露了你们接下来将要遭遇的麻烦。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=31; tag=开枪</t>
+    <t>源类型=type:txt_pb; 层级=31</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
-    <t>最终，杰森在愤恨交织下趁乱从你们手中逃走，而属于你们的任务也仍在继续。</t>
-  </si>
-  <si>
-    <t>loadScript(sntzm_clark3F(1), 1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=32; gotomainline=克拉克线3层（上）_1</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>源类型=type:exeBC; 层级=31</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>你的小聪明并没能逃过亚波伦的眼睛，他通过摄像头看清了你的花招，随后广播中爆发出一声尖锐的枪响。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_clark5_2,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=32; tag=不开枪</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>克拉克对幕后黑手杀害同伴的行为极为不忿，后者却大胆爆出了他的位置，邀请你们上去与其对峙。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=33</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>随即他挂断了通讯，一层的楼梯口处只剩下你们和吓破胆的杰森。你对杰森进行了进一步的问询，目标直指这家医院所进行的人体实验。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=34</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>随着他的再一次开口，圣诺汀尘封多年的黑暗秘密也终于露出冰山一角，而这仅仅只是这场游戏的开端。</t>
+    <t>最终，杰森在愤恨交织下趁乱从你们手中逃走，而属于你们的任务也仍在继续。仍</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -471,6 +618,60 @@
     </r>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=32; gotomainline=克拉克线3层（上）_1</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>jump(45)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=30; tag=不开枪</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>源类型=type:exeBC; 层级=31</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>你的小聪明并没能逃过亚波伦的眼睛，他通过摄像头看清了你的花招，随后广播中爆发出一声尖锐的枪响。</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_clark5_2,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=32; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"问艾米丽","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>克拉克对幕后黑手杀害同伴的行为极为不忿，后者却大胆爆出了他的位置，邀请你们上去与其对峙。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=33</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>随即他挂断了通讯，一层的楼梯口处只剩下你们和吓破胆的杰森。你对杰森进行了进一步的问询，目标直指这家医院所进行的人体实验。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=34</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>随着他的再一次开口，圣诺汀尘封多年的黑暗秘密也终于露出冰山一角，而这仅仅只是这场游戏的开端。</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=35; gotomainline=克拉克线3层（上）_1</t>
   </si>
   <si>
@@ -483,7 +684,7 @@
     <t>bgfade(sntzm_fourBranch2_52,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=32</t>
+    <t>源类型=type:txt_pb; 层级=32; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"问大卫","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
   </si>
   <si>
     <t>54</t>
@@ -504,6 +705,51 @@
     <t>35</t>
   </si>
   <si>
+    <t>jump(37)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=25; tag=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>问艾米丽</t>
+    </r>
+  </si>
+  <si>
     <t>37</t>
   </si>
   <si>
@@ -513,9 +759,6 @@
     <t>bgfade(sntzm_clark4_68,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=26; tag=问艾米莉</t>
-  </si>
-  <si>
     <t>38</t>
   </si>
   <si>
@@ -531,7 +774,7 @@
     <t>24</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=18; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"大卫线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=25</t>
+    <t>源类型=type:txt_pb; 层级=18; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"大卫线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
   </si>
   <si>
     <t>28</t>
@@ -588,15 +831,15 @@
     <t>不止如此，就连她自己的性命也岌岌可危，无线电内传来一阵急促的砸门声印证了她的说法。</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=25</t>
+  </si>
+  <si>
     <t>61</t>
   </si>
   <si>
     <t>在最后不到半分钟时间里，她接连说出了一些非常古怪的话，例如让你们不要相信名为“亚波伦”的男人，还提到了一个名叫“纳丁达克”的公司。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=26</t>
-  </si>
-  <si>
     <t>62</t>
   </si>
   <si>
@@ -616,6 +859,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -642,19 +890,19 @@
     <t>20</t>
   </si>
   <si>
-    <t>jump(21)</t>
+    <t>源类型=type:txt_pb; 层级=15; tag=大卫线; gotomainline=21</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>jump(14)</t>
+    <t>源类型=type:txt_pb; 层级=10; tag=夜莺线; gotomainline=14</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>jump(9)</t>
+    <t>源类型=type:txt_pb; 层级=6; tag=隐瞒; gotomainline=9</t>
   </si>
   <si>
     <t>项目</t>
@@ -672,7 +920,7 @@
     <t>转换时间</t>
   </si>
   <si>
-    <t>2026/9/21 11:34:58</t>
+    <t>2026/9/21 17:07:36</t>
   </si>
   <si>
     <t>输出节点数</t>
@@ -699,13 +947,13 @@
     <t>datatype=type:txt_* -&gt; 按 节点类型转中文.xlsx 的 Type/Name 映射生成 Speaker</t>
   </si>
   <si>
-    <t>selectBC 子节点 -&gt; Command 中的 choice(文本|jump(分支首句ID))</t>
+    <t>selectBC 子节点 -&gt; Command 中的 choice(文本|jump(选项入口ID))</t>
   </si>
   <si>
     <t>selectBC 直接子节点作为选项入口时，不再把选项文字写入 Text</t>
   </si>
   <si>
-    <t>选项入口 Note 除源类型/层级外，其余字段追加到分支首句 Note</t>
+    <t>选项入口保留自身 tag 等 Note 字段；Command 优先使用 gotomainline，否则 jump 到第一个子节点</t>
   </si>
   <si>
     <t>gotomainline 数字 -&gt; jump(ID)；文件名_数字 -&gt; loadScript(文件名, 数字)；其他非数字 -&gt; loadScript(文件名, 1)</t>
@@ -2438,7 +2686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" ht="30" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2464,21 +2712,21 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="57" spans="1:12">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -2496,7 +2744,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -2508,15 +2756,15 @@
         <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" ht="30" spans="1:12">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2534,7 +2782,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2546,15 +2794,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="42" spans="1:12">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2572,7 +2820,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2587,12 +2835,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2610,7 +2858,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2625,12 +2873,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2660,15 +2908,15 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2698,15 +2946,15 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="55.5" spans="1:12">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2724,7 +2972,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2736,15 +2984,15 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2762,7 +3010,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2777,12 +3025,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:12">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2812,15 +3060,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2850,15 +3098,15 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="L12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -2891,12 +3139,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" ht="103.5" spans="1:12">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" ht="90" spans="1:12">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2914,7 +3162,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -2926,15 +3174,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="90" spans="1:12">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2952,7 +3200,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -2963,13 +3211,16 @@
       <c r="J15" t="s">
         <v>15</v>
       </c>
+      <c r="K15" t="s">
+        <v>15</v>
+      </c>
       <c r="L15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="40.5" spans="1:12">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -2987,7 +3238,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -2999,15 +3250,15 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:12">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3037,15 +3288,15 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3075,15 +3326,15 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="L18" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="69" spans="1:12">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3101,7 +3352,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3113,15 +3364,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L19" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3154,12 +3405,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" ht="90" spans="1:12">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3177,7 +3428,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3189,15 +3440,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L21" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" ht="40.5" spans="1:12">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3215,7 +3466,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3230,12 +3481,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="57" spans="1:12">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3252,8 +3503,8 @@
       <c r="F23" t="s">
         <v>15</v>
       </c>
-      <c r="G23" t="s">
-        <v>82</v>
+      <c r="G23" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3265,15 +3516,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L23" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3291,7 +3542,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3303,15 +3554,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="L24" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="28.5" spans="1:12">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3329,7 +3580,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3341,15 +3592,15 @@
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="55.5" spans="1:12">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3366,8 +3617,8 @@
       <c r="F26" t="s">
         <v>15</v>
       </c>
-      <c r="G26" t="s">
-        <v>94</v>
+      <c r="G26" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3382,12 +3633,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="45" spans="1:12">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3416,16 +3667,16 @@
       <c r="J27" t="s">
         <v>15</v>
       </c>
-      <c r="K27" t="s">
-        <v>97</v>
+      <c r="K27" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="L27" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3455,15 +3706,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>15</v>
-      </c>
-      <c r="L28" t="s">
-        <v>100</v>
+        <v>105</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="29" ht="70.5" spans="1:12">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3481,7 +3732,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3493,15 +3744,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L29" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:12">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3519,7 +3770,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3534,12 +3785,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3557,7 +3808,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3572,12 +3823,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:12">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3607,15 +3858,15 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="L32" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3645,15 +3896,15 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="L33" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" ht="40.5" spans="1:12">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3671,7 +3922,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3686,12 +3937,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" ht="30" spans="1:12">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3708,8 +3959,8 @@
       <c r="F35" t="s">
         <v>15</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>120</v>
+      <c r="G35" t="s">
+        <v>127</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3720,16 +3971,16 @@
       <c r="J35" t="s">
         <v>15</v>
       </c>
-      <c r="K35" t="s">
-        <v>121</v>
+      <c r="K35" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="L35" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -3759,15 +4010,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="L36" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3800,12 +4051,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="38" ht="40.5" spans="1:12">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" ht="90" spans="1:12">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -3823,7 +4074,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -3835,15 +4086,15 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L38" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" ht="27" spans="1:12">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -3861,7 +4112,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -3876,12 +4127,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -3899,7 +4150,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -3914,12 +4165,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" ht="40.5" spans="1:12">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -3937,7 +4188,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -3949,15 +4200,15 @@
         <v>15</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L41" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="42" ht="54" spans="1:12">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="42" ht="90" spans="1:12">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -3975,7 +4226,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -3987,15 +4238,15 @@
         <v>15</v>
       </c>
       <c r="K42" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="L42" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" ht="45" spans="1:12">
       <c r="A43" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4013,7 +4264,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4028,12 +4279,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" ht="40.5" spans="1:12">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4051,7 +4302,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4063,15 +4314,15 @@
         <v>15</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L44" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4101,15 +4352,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>15</v>
-      </c>
-      <c r="L45" t="s">
-        <v>100</v>
+        <v>158</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="46" ht="54" spans="1:12">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4127,7 +4378,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4139,15 +4390,15 @@
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="L46" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" ht="40.5" spans="1:12">
       <c r="A47" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4165,7 +4416,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4177,15 +4428,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="L47" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" ht="90" spans="1:12">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4203,7 +4454,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4214,13 +4465,16 @@
       <c r="J48" t="s">
         <v>15</v>
       </c>
+      <c r="K48" t="s">
+        <v>15</v>
+      </c>
       <c r="L48" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4238,7 +4492,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4253,12 +4507,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4276,7 +4530,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4288,15 +4542,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="L50" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" ht="54" spans="1:12">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4314,7 +4568,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4326,15 +4580,15 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="L51" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4352,7 +4606,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4364,15 +4618,15 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="L52" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" ht="55.5" spans="1:12">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4390,7 +4644,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4402,15 +4656,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="L53" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" ht="55.5" spans="1:12">
       <c r="A54" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4428,7 +4682,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4443,12 +4697,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4466,7 +4720,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4481,12 +4735,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>100</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" ht="43.5" spans="1:12">
       <c r="A56" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4504,7 +4758,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4519,12 +4773,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" ht="28.5" spans="1:12">
       <c r="A57" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4542,7 +4796,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4557,12 +4811,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" ht="54" spans="1:12">
       <c r="A58" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4579,8 +4833,8 @@
       <c r="F58" t="s">
         <v>15</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>184</v>
+      <c r="G58" t="s">
+        <v>193</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4595,12 +4849,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4618,7 +4872,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4630,15 +4884,15 @@
         <v>15</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="L59" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4668,15 +4922,15 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>190</v>
+        <v>71</v>
       </c>
       <c r="L60" t="s">
-        <v>67</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4706,15 +4960,15 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>192</v>
+        <v>52</v>
       </c>
       <c r="L61" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4744,10 +4998,10 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>194</v>
+        <v>39</v>
       </c>
       <c r="L62" t="s">
-        <v>37</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4768,122 +5022,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B11" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" ht="58.5" spans="1:2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" ht="88.5" spans="1:2">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B13" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B15" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -4905,616 +5159,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D2" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="E2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F3" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D4" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E4" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="F4" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D5" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="F5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D6" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F6" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C7" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E7" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F7" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B8" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D8" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="E8" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="F8" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B9" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C9" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D9" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E9" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="F9" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B10" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C10" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="D10" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="E10" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="F10" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B11" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C11" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D11" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E11" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="F11" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B12" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C12" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E12" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F12" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B13" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="C13" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="E13" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="F13" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C14" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="D14" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="E14" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F14" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B15" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D15" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E15" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F15" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B16" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C16" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D16" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="E16" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F16" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B17" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C17" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D17" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="E17" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="F17" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B18" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C18" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D18" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="E18" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="F18" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B19" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C19" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D19" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="E19" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F19" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B20" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C20" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D20" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="E20" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="F20" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B21" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C21" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D21" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E21" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F21" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B22" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C22" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="D22" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="E22" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="F22" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C23" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D23" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="E23" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F23" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="C24" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D24" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="E24" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="F24" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B25" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C25" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="D25" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="E25" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="F25" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B26" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C26" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D26" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="E26" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="F26" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B27" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C27" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="D27" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="E27" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="F27" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B28" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="C28" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D28" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="E28" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F28" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B29" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C29" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D29" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E29" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F29" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B30" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="C30" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="D30" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="E30" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F30" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B31" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C31" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="D31" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
